--- a/GWD Data/PVC on Wall PRICE.xlsx
+++ b/GWD Data/PVC on Wall PRICE.xlsx
@@ -854,7 +854,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <tabColor rgb="FFFF0000"/>
+    <tabColor rgb="FFFF00FF"/>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
@@ -6949,9 +6949,7 @@
       <c r="F345" s="12"/>
       <c r="G345" s="4"/>
       <c r="H345" s="5"/>
-      <c r="I345" s="33">
-        <v>1.0</v>
-      </c>
+      <c r="I345" s="33"/>
     </row>
     <row r="346">
       <c r="A346" s="10" t="s">
@@ -6966,9 +6964,7 @@
       <c r="F346" s="3"/>
       <c r="G346" s="4"/>
       <c r="H346" s="5"/>
-      <c r="I346" s="33">
-        <v>2.0</v>
-      </c>
+      <c r="I346" s="33"/>
     </row>
     <row r="347">
       <c r="A347" s="14" t="s">

--- a/GWD Data/PVC on Wall PRICE.xlsx
+++ b/GWD Data/PVC on Wall PRICE.xlsx
@@ -1035,7 +1035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38925A53-0873-48DA-A61C-BC3B6EE4B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0963BA10-1CA3-428E-8B16-EFA46DFCB9A6}">
   <dimension ref="A1:G947"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/PVC on Wall PRICE.xlsx
+++ b/GWD Data/PVC on Wall PRICE.xlsx
@@ -165,7 +165,7 @@
     <t>MR41</t>
   </si>
   <si>
-    <t>PVC pipe 20 mm outer dia 10 kfg/cm2
+    <t>PVC pipe 20 mm outer dia 10 kgf/cm2
 (Adding 15% for fittings wastage)</t>
   </si>
   <si>
@@ -228,7 +228,7 @@
 Add 15% for fitting and wastage etc on (A)</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes, fittings including fixing the pipe with clamps at 1.00 m spacing. This includes jointing of pipes &amp; fittings with one step PVC solvent cement and testing of joints complete as per direction of Engineer-in-Charge 50 mm dia 10 Kfg/cm - Internal work- Exposed on wall (50.18.7.6.1)</t>
+    <t>Providing and fixing PVC pipes, fittings including fixing the pipe with clamps at 1.00 m spacing. This includes jointing of pipes &amp; fittings with one step PVC solvent cement and testing of joints complete as per direction of Engineer-in-Charge 50 mm dia 10 kgf/cm - Internal work- Exposed on wall (50.18.7.6.1)</t>
   </si>
   <si>
     <t>MR48</t>
@@ -374,7 +374,7 @@
 Adhesive, and sundries etc</t>
   </si>
   <si>
-    <t>Providing and fixing PVC pipes including fixing the pipe with clamps/Clips at 1.00 m spacing. This included jointing of pipes with one step PVC solvent cement and testing of joints complete as per direction of Engineer-in-Charge 75 mm dia 4 Kfg/cm2 - External work - Exposed on wall (50.18.9.18.2)</t>
+    <t>Providing and fixing PVC pipes including fixing the pipe with clamps/Clips at 1.00 m spacing. This included jointing of pipes with one step PVC solvent cement and testing of joints complete as per direction of Engineer-in-Charge 75 mm dia 4 kgf/cm2 - External work - Exposed on wall (50.18.9.18.2)</t>
   </si>
   <si>
     <t>MR53</t>
@@ -1035,7 +1035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0963BA10-1CA3-428E-8B16-EFA46DFCB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7E4E814-48B5-4F4B-B3F5-AD51A955B9A6}">
   <dimension ref="A1:G947"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
